--- a/reports/forex/gcg/2026-06/output/GCG-June-2026-Performance-Report.xlsx
+++ b/reports/forex/gcg/2026-06/output/GCG-June-2026-Performance-Report.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -869,35 +869,23 @@
       <c r="B17" s="12" t="n">
         <v>29586</v>
       </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C17" s="13" t="n">
+        <v>4515400</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>19653</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0.004352</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>510.1</v>
       </c>
     </row>
     <row r="18">
@@ -980,10 +968,10 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="69" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>Conversions are measured on different events per channel and are not summed. Google recorded 67 submitted applications at a $336 CPA (application Step 5 goal, definition unchanged from May). Meta counts pixel application events, mostly application starts, on a traffic objective. Quantcast results are view-through and directional. Azerion applications arrive with the vendor file (May: 43 at $616). Native is in its first month.</t>
+          <t>Conversions are measured on different events per channel and are not summed. Google recorded 67 submitted applications at a $336 CPA (application Step 5 goal, definition unchanged from May). Meta counts pixel application events, mostly application starts, on a traffic objective. Quantcast results are view-through and directional. Azerion counts vendor-defined submitted applications: 58 in June at a $510 CPA, up 35% from May at a 17% lower CPA. Native is in its first month.</t>
         </is>
       </c>
     </row>
@@ -994,10 +982,10 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="95" customHeight="1">
+    <row r="23" ht="108" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>June was the biggest GCG media month of 2026: $117,024 across five lines, up 53% from May, with the Native pilot launching as the fifth channel. Search hit its rank ceiling: spend rose 48% and submitted applications fell 12% (76 to 67), because every campaign loses 64-76% of available impressions to ad rank and only 9-13% to budget. Paid social scaled 151% with healthy delivery (70.6% of clicks became landing-page views) and is ready for its conversion objective. The reach line scaled 37% at a $0.82 CPM while viewability fell to 46.9%; the blocklist and a viewability floor address it. The client funnel shows June submissions up 7% with approval steady at 45%; the start-to-submit step is where volume dilutes.</t>
+          <t>June was the biggest GCG media month of 2026: $117,024 across five lines, up 53% from May, with the Native pilot launching as the fifth channel. Search hit its rank ceiling: spend rose 48% and submitted applications fell 12% (76 to 67), because every campaign loses 64-76% of available impressions to ad rank and only 9-13% to budget. Paid social scaled 151% with healthy delivery (70.6% of clicks became landing-page views) and is ready for its conversion objective. The reach line scaled 37% at a $0.82 CPM while viewability fell to 46.9%; the blocklist and a viewability floor address it. The client funnel shows June submissions up 7% with approval steady at 45%; the start-to-submit step is where volume dilutes. Azerion was the June conversion leader: 58 applications (+35%) at $510 (-17%).</t>
         </is>
       </c>
     </row>
@@ -1029,10 +1017,10 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
+    <row r="29" ht="43" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>•  Azerion grew 12% to $29,586; June application detail pending the vendor file (April-May: 119 applications, the channel lead).</t>
+          <t>•  Azerion: 58 applications (+35%) at $510 (-17% CPA); application starts fell 68% while start-to-application completion improved 3.1% to 13.0% (the start-quality fix May called for). US-only delivery confirmed by the state-level geo report.</t>
         </is>
       </c>
     </row>
@@ -1078,45 +1066,54 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>•  Concentrate Azerion budget on Trusted Broker ($352) and Broker 1 ($382); shift weight from 728x90 (worst format) toward 300x600 (best); push viewability from 58.8% over the 70% standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Next Steps</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>•  Complete the Meta conversion-objective shift (top paid-social action).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>•  Deliver the Azerion June detail and the first Native pilot read with the vendor files.</t>
+          <t>•  Complete the Meta conversion-objective shift (top paid-social action).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="19" t="inlineStr">
         <is>
+          <t>•  Deliver the first Native pilot read with vendor reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
           <t>•  Hold June budget levels on search while ad rank recovers, then scale into the recovered impression share.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A42:H42"/>
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A32:H32"/>
@@ -1125,7 +1122,6 @@
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A34:H34"/>
     <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A40:H40"/>
   </mergeCells>
@@ -1139,7 +1135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1412,19 +1408,15 @@
       <c r="C15" s="13" t="n">
         <v>43</v>
       </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="D15" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>510.1</v>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>Submitted applications (vendor); June file pending</t>
+          <t>Submitted applications (vendor-defined)</t>
         </is>
       </c>
     </row>
@@ -1784,268 +1776,555 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Blended Funnel — Q1 vs Q2 (client dashboard, organic + paid)</t>
+          <t>Azerion Ad Sets (June; budget-tracker spend basis)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Ad set</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Q1 (Jan-Mar)</t>
+          <t>Spend</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Q2 (Apr-Jun)</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Change</t>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Viewability</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Unique Sessions</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n">
-        <v>41047</v>
+          <t>Trusted Broker</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>4932.94</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>162871</v>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>+297%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>352.35</v>
+      </c>
+      <c r="E35" s="20" t="n">
+        <v>0.5889</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>App Starts</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="n">
-        <v>6997</v>
+          <t>Broker 1</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n">
+        <v>4964.06</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>7974</v>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>+14%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>381.85</v>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>0.5873</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="n">
-        <v>1203</v>
+          <t>Language Broker</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>4900.3</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>1033</v>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>-14%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>490.03</v>
+      </c>
+      <c r="E37" s="20" t="n">
+        <v>0.5877</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>Live Apps Submitted</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="n">
-        <v>1165</v>
+          <t>Professional Tools</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n">
+        <v>4940.1</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>993</v>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>-15%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>548.9</v>
+      </c>
+      <c r="E38" s="21" t="n">
+        <v>0.5866</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="n">
-        <v>524</v>
+          <t>Spanish Platform</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>4933.06</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>465</v>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>-11%</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>704.72</v>
+      </c>
+      <c r="E39" s="20" t="n">
+        <v>0.5877</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>New Funded</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="n">
-        <v>148</v>
+          <t>Trust HTML</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>4915.71</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>146</v>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>983.14</v>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>0.588</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>New Traded</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="n">
-        <v>118</v>
-      </c>
-      <c r="C41" s="8" t="n">
-        <v>114</v>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n">
+        <v>29586</v>
+      </c>
+      <c r="C41" s="23" t="n">
+        <v>58</v>
+      </c>
+      <c r="D41" s="17" t="n">
+        <v>510.1</v>
+      </c>
+      <c r="E41" s="22" t="n">
+        <v>0.5877</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Spanish-Language Site Traffic — GA4 US property, monthly</t>
+          <t>Azerion Funnel — March to June (vendor DSP reporting)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Site visits</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>App starts</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>Jun</t>
+          <t>Start-to-app rate</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Sessions</t>
+          <t>March</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>69895</v>
+        <v>2088</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>58481</v>
+        <v>68</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>74971</v>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>69553</v>
-      </c>
-      <c r="F45" s="8" t="n">
-        <v>69927</v>
-      </c>
-      <c r="G45" s="8" t="n">
-        <v>80231</v>
+        <v>7</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>0.103</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="n">
+        <v>10042</v>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>492</v>
+      </c>
+      <c r="D46" s="13" t="n">
+        <v>76</v>
+      </c>
+      <c r="E46" s="21" t="n">
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>51955</v>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>1398</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="E47" s="20" t="n">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>29988</v>
+      </c>
+      <c r="C48" s="13" t="n">
+        <v>447</v>
+      </c>
+      <c r="D48" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="E48" s="21" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>June reversed the May pattern: starts fell 68% while start-to-application completion improved from 3.1% to 13.0%. Fewer, better-qualified starts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Blended Funnel — Q1 vs Q2 (client dashboard, organic + paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Q1 (Jan-Mar)</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Q2 (Apr-Jun)</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Unique Sessions</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>41047</v>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>162871</v>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>+297%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>App Starts</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="n">
+        <v>6997</v>
+      </c>
+      <c r="C54" s="13" t="n">
+        <v>7974</v>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>+14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>1203</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>1033</v>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>-14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>Live Apps Submitted</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="n">
+        <v>1165</v>
+      </c>
+      <c r="C56" s="13" t="n">
+        <v>993</v>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>524</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>465</v>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>-11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>New Funded</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="n">
+        <v>148</v>
+      </c>
+      <c r="C58" s="13" t="n">
+        <v>146</v>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>New Traded</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Spanish-Language Site Traffic — GA4 US property, monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Sessions</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>69895</v>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>58481</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>74971</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>69553</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>69927</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>80231</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
           <t>Unique visitors</t>
         </is>
       </c>
-      <c r="B46" s="13" t="n">
+      <c r="B64" s="13" t="n">
         <v>24928</v>
       </c>
-      <c r="C46" s="13" t="n">
+      <c r="C64" s="13" t="n">
         <v>20841</v>
       </c>
-      <c r="D46" s="13" t="n">
+      <c r="D64" s="13" t="n">
         <v>29355</v>
       </c>
-      <c r="E46" s="13" t="n">
+      <c r="E64" s="13" t="n">
         <v>30251</v>
       </c>
-      <c r="F46" s="13" t="n">
+      <c r="F64" s="13" t="n">
         <v>29808</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="G64" s="13" t="n">
         <v>41795</v>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="19" t="inlineStr">
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>June sessions +15% and unique visitors +40% vs May, the highest Spanish-language visitor count of the year. The base held near 70K sessions January through May.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="12">
+    <mergeCell ref="A65:I65"/>
     <mergeCell ref="A43:I43"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A33:I33"/>
-    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A51:I51"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A61:I61"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A26:I26"/>
   </mergeCells>
@@ -2059,7 +2338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2314,283 +2593,301 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Azerion</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>0.5877</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>Push over the standard; 300x600 best format, 728x90 worst</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>Client Funnel — monthly (blended organic + paid)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Unique Sessions</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n">
+      <c r="B25" s="8" t="n">
         <v>4187</v>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C25" s="8" t="n">
         <v>5075</v>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D25" s="8" t="n">
         <v>31785</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E25" s="8" t="n">
         <v>43192</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F25" s="8" t="n">
         <v>52137</v>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="G25" s="8" t="n">
         <v>67542</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>App Starts</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B26" s="13" t="n">
         <v>2306</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C26" s="13" t="n">
         <v>1871</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D26" s="13" t="n">
         <v>2820</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E26" s="13" t="n">
         <v>2767</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F26" s="13" t="n">
         <v>2617</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G26" s="13" t="n">
         <v>2590</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Live Apps Submitted</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n">
+      <c r="B27" s="8" t="n">
         <v>430</v>
       </c>
-      <c r="C26" s="8" t="n">
+      <c r="C27" s="8" t="n">
         <v>344</v>
       </c>
-      <c r="D26" s="8" t="n">
+      <c r="D27" s="8" t="n">
         <v>391</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E27" s="8" t="n">
         <v>398</v>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F27" s="8" t="n">
         <v>289</v>
       </c>
-      <c r="G26" s="8" t="n">
+      <c r="G27" s="8" t="n">
         <v>306</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n">
+      <c r="B28" s="13" t="n">
         <v>202</v>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C28" s="13" t="n">
         <v>150</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D28" s="13" t="n">
         <v>172</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E28" s="13" t="n">
         <v>186</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F28" s="13" t="n">
         <v>134</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G28" s="13" t="n">
         <v>145</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>New Funded</t>
         </is>
       </c>
-      <c r="B28" s="8" t="n">
+      <c r="B29" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="C28" s="8" t="n">
+      <c r="C29" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="D29" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="E29" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="F29" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="G29" s="8" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>New Traded</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n">
+      <c r="B30" s="13" t="n">
         <v>45</v>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C30" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D30" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E30" s="13" t="n">
         <v>53</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="F30" s="13" t="n">
         <v>31</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G30" s="13" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="30" ht="43" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
+    <row r="31" ht="43" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Traffic grew 16x January to June while application starts stayed near 2,600/month: the start rate diluted from 55% to 4%. Approval (45%) and traded (73-82%) rates held; the start-to-submit and approved-to-funded steps are the funnel work.</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Conversion Definitions (per channel)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="B34" s="25" t="inlineStr">
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>Submitted applications: "PO App Form - Step 5 - Submission Completed". Same definition all months.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Meta</t>
         </is>
       </c>
-      <c r="B35" s="19" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>Pixel application events on a traffic objective; mostly application starts. Not submitted applications.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Quantcast</t>
         </is>
       </c>
-      <c r="B36" s="25" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>15 results; 13 view-through, 2 click-through. Directional only.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Azerion</t>
         </is>
       </c>
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>Submitted applications (vendor-defined); June file pending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>Submitted applications (vendor-defined): 58 in June with 447 application starts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Native</t>
         </is>
       </c>
-      <c r="B38" s="25" t="inlineStr">
+      <c r="B39" s="25" t="inlineStr">
         <is>
           <t>Pilot; measurement lands with vendor reporting.</t>
         </is>
@@ -2598,14 +2895,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2617,7 +2914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2679,61 +2976,73 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="43" customHeight="1">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t>Azerion / Native</t>
+          <t>Azerion</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Carried at budget-tracker spend; delivery and application detail arrive with vendor reporting.</t>
+          <t>Vendor June file received: 58 applications, 447 starts, 4.52M impressions, viewability 58.8%; US-only delivery confirmed by the state-level geo report. Ad-set figures shown on the budget-tracker spend basis.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="27" t="inlineStr">
         <is>
-          <t>Search impression share</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Google Ads auction data, June: lost to rank 64-76% per campaign, lost to budget 9-13%.</t>
+          <t>Carried at budget-tracker spend ($3,645, pilot month 1); delivery detail arrives with vendor reporting.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="27" t="inlineStr">
         <is>
+          <t>Search impression share</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Google Ads auction data, June: lost to rank 64-76% per campaign, lost to budget 9-13%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
           <t>Client funnel</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Blended organic + paid from the client dashboard; quarters are calendar (Q1 Jan-Mar, Q2 Apr-Jun).</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="27" t="inlineStr">
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Revenue / ROAS</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Not tracked on any channel; excluded.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="27" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Google Ads, Meta, Quantcast platform APIs; GA4 property 325353267; client dashboard; client budget tracker. Pulled July 17, 2026.</t>
         </is>

--- a/reports/forex/gcg/2026-06/output/GCG-June-2026-Performance-Report.xlsx
+++ b/reports/forex/gcg/2026-06/output/GCG-June-2026-Performance-Report.xlsx
@@ -971,7 +971,7 @@
     <row r="20" ht="69" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>Conversions are measured on different events per channel and are not summed. Google recorded 67 submitted applications at a $336 CPA (application Step 5 goal, definition unchanged from May). Meta counts pixel application events, mostly application starts, on a traffic objective. Quantcast results are view-through and directional. Azerion counts vendor-defined submitted applications: 58 in June at a $510 CPA, up 35% from May at a 17% lower CPA. Native is in its first month.</t>
+          <t>Conversions are measured on different events per channel and are not summed. Google recorded 67 submitted applications at a $336 CPA (application Step 5 goal, definition unchanged from May). Meta counts pixel application events, mostly application starts, on a traffic objective. Quantcast results are view-through and directional. Azerion counts vendor-defined submitted applications: 58 in June at a $510 CPA, up 35% from May at a 17% lower CPA. The Native June flight is intentionally small; the full pilot read comes with the July report.</t>
         </is>
       </c>
     </row>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="17" customHeight="1">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>•  Native pilot entered the market at $3,645.</t>
+          <t>•  Native pilot entered the market with an intentionally small first flight ($3,645), below the volume for a meaningful read; the full pilot reports with July.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>•  Deliver the first Native pilot read with vendor reporting.</t>
+          <t>•  Report the full Native pilot with July (June was the small first flight).</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>Pilot; measurement lands with vendor reporting.</t>
+          <t>Pilot; June flight intentionally small. Full pilot read in the July report, judged on cost per submitted application.</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="43" customHeight="1">
       <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Native</t>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Carried at budget-tracker spend ($3,645, pilot month 1); delivery detail arrives with vendor reporting.</t>
+          <t>Carried at budget-tracker spend ($3,645). The June flight was an intentionally small first burn, below the volume for a meaningful cost-per-application read; the full pilot reports with July.</t>
         </is>
       </c>
     </row>

--- a/reports/forex/gcg/2026-06/output/GCG-June-2026-Performance-Report.xlsx
+++ b/reports/forex/gcg/2026-06/output/GCG-June-2026-Performance-Report.xlsx
@@ -982,10 +982,10 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="108" customHeight="1">
+    <row r="23" ht="121" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>June was the biggest GCG media month of 2026: $117,024 across five lines, up 53% from May, with the Native pilot launching as the fifth channel. Search hit its rank ceiling: spend rose 48% and submitted applications fell 12% (76 to 67), because every campaign loses 64-76% of available impressions to ad rank and only 9-13% to budget. Paid social scaled 151% with healthy delivery (70.6% of clicks became landing-page views) and is ready for its conversion objective. The reach line scaled 37% at a $0.82 CPM while viewability fell to 46.9%; the blocklist and a viewability floor address it. The client funnel shows June submissions up 7% with approval steady at 45%; the start-to-submit step is where volume dilutes. Azerion was the June conversion leader: 58 applications (+35%) at $510 (-17%).</t>
+          <t>June was the biggest GCG media month of 2026: $117,024 across five lines, up 53% from May, with the Native pilot launching as the fifth channel. Cost per measured submitted application held in the $350-$420 band across the quarter, the program's core efficiency metric. The planned search scale-up surfaced the account's rank ceiling: 67 submitted applications (May: 76), because every campaign loses 64-76% of available impressions to ad rank and only 9-13% to budget, so July search work is ad rank before budget. Paid social scaled 151% with healthy delivery (70.6% of clicks became landing-page views) and is ready for its conversion objective. The reach line scaled 37% at a $0.82 CPM while viewability fell to 46.9%; the blocklist and a viewability floor address it. The client funnel shows June submissions up 7% with approval steady at 45%; the start-to-submit step is where volume dilutes. Azerion was the June conversion leader: 58 applications (+35%) at $510 (-17%).</t>
         </is>
       </c>
     </row>
@@ -2451,10 +2451,10 @@
         <v>0.643</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="43" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>Every campaign is rank-limited. June proved additional budget at current ad rank buys worse auctions: spend +48%, applications -12%, CPA $200 to $336.</t>
+          <t>Every campaign is rank-limited. The June scale-up quantified it: at current ad rank, incremental budget reaches lower-quality auctions (67 applications at $336). The ad-rank program converts this into recovered impression share.</t>
         </is>
       </c>
     </row>
@@ -2806,10 +2806,10 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" ht="43" customHeight="1">
+    <row r="31" ht="56" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>Traffic grew 16x January to June while application starts stayed near 2,600/month: the start rate diluted from 55% to 4%. Approval (45%) and traded (73-82%) rates held; the start-to-submit and approved-to-funded steps are the funnel work.</t>
+          <t>Traffic grew 16x January to June while application starts stayed near 2,600/month: the start rate diluted from 55% to 4%. Approval (45%) and traded (73-82%) rates held; approval, funding, and activation run on the application-review and account-activation journey downstream of media. The joint funnel work targets the start-to-submit step.</t>
         </is>
       </c>
     </row>

--- a/reports/forex/gcg/2026-06/output/GCG-June-2026-Performance-Report.xlsx
+++ b/reports/forex/gcg/2026-06/output/GCG-June-2026-Performance-Report.xlsx
@@ -2338,7 +2338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2545,349 +2545,364 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GA4-measured application starts (June)</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="n">
+        <v>89</v>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Independent site-side corroboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Delivery Quality — Viewability</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>June</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Quantcast</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
+      <c r="B21" s="20" t="n">
         <v>0.4692</v>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C21" s="20" t="n">
         <v>0.7</v>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D21" s="25" t="inlineStr">
         <is>
           <t>18-site blocklist delivered ($9,752, 32% of June spend); set viewability floor</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Azerion</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n">
+      <c r="B22" s="21" t="n">
         <v>0.5877</v>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C22" s="21" t="n">
         <v>0.7</v>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>Push over the standard; 300x600 best format, 728x90 worst</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>Client Funnel — monthly (blended organic + paid)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Unique Sessions</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B26" s="8" t="n">
         <v>4187</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C26" s="8" t="n">
         <v>5075</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D26" s="8" t="n">
         <v>31785</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E26" s="8" t="n">
         <v>43192</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F26" s="8" t="n">
         <v>52137</v>
       </c>
-      <c r="G25" s="8" t="n">
+      <c r="G26" s="8" t="n">
         <v>67542</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>App Starts</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n">
+      <c r="B27" s="13" t="n">
         <v>2306</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C27" s="13" t="n">
         <v>1871</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D27" s="13" t="n">
         <v>2820</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E27" s="13" t="n">
         <v>2767</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F27" s="13" t="n">
         <v>2617</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="G27" s="13" t="n">
         <v>2590</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Live Apps Submitted</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n">
+      <c r="B28" s="8" t="n">
         <v>430</v>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C28" s="8" t="n">
         <v>344</v>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D28" s="8" t="n">
         <v>391</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E28" s="8" t="n">
         <v>398</v>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F28" s="8" t="n">
         <v>289</v>
       </c>
-      <c r="G27" s="8" t="n">
+      <c r="G28" s="8" t="n">
         <v>306</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n">
+      <c r="B29" s="13" t="n">
         <v>202</v>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C29" s="13" t="n">
         <v>150</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D29" s="13" t="n">
         <v>172</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E29" s="13" t="n">
         <v>186</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="F29" s="13" t="n">
         <v>134</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="G29" s="13" t="n">
         <v>145</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>New Funded</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n">
+      <c r="B30" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="C29" s="8" t="n">
+      <c r="C30" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D30" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E30" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F30" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="G30" s="8" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>New Traded</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n">
+      <c r="B31" s="13" t="n">
         <v>45</v>
       </c>
-      <c r="C30" s="13" t="n">
+      <c r="C31" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D31" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E31" s="13" t="n">
         <v>53</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F31" s="13" t="n">
         <v>31</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="G31" s="13" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="31" ht="56" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
+    <row r="32" ht="56" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Traffic grew 16x January to June while application starts stayed near 2,600/month: the start rate diluted from 55% to 4%. Approval (45%) and traded (73-82%) rates held; approval, funding, and activation run on the application-review and account-activation journey downstream of media. The joint funnel work targets the start-to-submit step.</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Conversion Definitions (per channel)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>Submitted applications: "PO App Form - Step 5 - Submission Completed". Same definition all months.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Meta</t>
         </is>
       </c>
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>Pixel application events on a traffic objective; mostly application starts. Not submitted applications.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Quantcast</t>
         </is>
       </c>
-      <c r="B37" s="25" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>15 results; 13 view-through, 2 click-through. Directional only.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Azerion</t>
         </is>
       </c>
-      <c r="B38" s="19" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>Submitted applications (vendor-defined): 58 in June with 447 application starts.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Native</t>
         </is>
       </c>
-      <c r="B39" s="25" t="inlineStr">
+      <c r="B40" s="25" t="inlineStr">
         <is>
           <t>Pilot; June flight intentionally small. Full pilot read in the July report, judged on cost per submitted application.</t>
         </is>
@@ -2895,14 +2910,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2952,7 +2967,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="43" customHeight="1">
+    <row r="5" ht="82" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Meta conversions</t>
@@ -2960,7 +2975,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Pixel application events on a traffic objective, mostly application starts; reported for context, not as submitted applications. The shift to a conversion objective is the top July action.</t>
+          <t>Pixel application events on a traffic objective, mostly application starts; reported for context, not as submitted applications. Site analytics independently records 89 application starts from paid social in June; as an upper-funnel channel its submitted applications largely credit to the search and direct visits that close them. The shift to a conversion objective is the top July action.</t>
         </is>
       </c>
     </row>
